--- a/mini campionato di testa 26-27.xlsx
+++ b/mini campionato di testa 26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\--- fantacalcio tot uff\26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE8F70F-19E7-49D4-9388-E03E50870401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF0D09A-606F-43B8-B1BC-C450D11E58D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="23">
   <si>
     <t>atalanta</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>2-2</t>
+  </si>
+  <si>
+    <t>5-3</t>
   </si>
 </sst>
 </file>
@@ -554,36 +557,36 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="M4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4" s="1">
         <f>SUM(O4:Q4)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4" s="1">
         <v>1</v>
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="S4" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T4" s="1">
         <f>SUM(R4-S4)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U4" s="1">
         <f>SUM((O4*3)+P4)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <f>SUM(U4+T4*0.001+R4*0.00001)</f>
-        <v>4.0010400000000006</v>
+        <v>7.0030999999999999</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -602,7 +605,7 @@
         <v>18</v>
       </c>
       <c r="M5" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="N5" s="1">
         <f>SUM(O5:Q5)</f>
@@ -616,10 +619,10 @@
       </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" s="1">
         <f>SUM(R5-S5)</f>
@@ -631,7 +634,7 @@
       </c>
       <c r="V5">
         <f>SUM(U5+T5*0.001+R5*0.00001)</f>
-        <v>4.0010300000000001</v>
+        <v>4.0010400000000006</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -646,26 +649,30 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="I6" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="7"/>
       <c r="M6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N6" s="1">
         <f>SUM(O6:Q6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" s="1">
         <v>1</v>
       </c>
-      <c r="P6" s="1"/>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
       <c r="Q6" s="1"/>
       <c r="R6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T6" s="1">
         <f>SUM(R6-S6)</f>
@@ -673,11 +680,11 @@
       </c>
       <c r="U6" s="1">
         <f>SUM((O6*3)+P6)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V6">
         <f>SUM(U6+T6*0.001+R6*0.00001)</f>
-        <v>3.0010300000000001</v>
+        <v>4.0010400000000006</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -696,22 +703,24 @@
       <c r="J7" s="3"/>
       <c r="K7" s="7"/>
       <c r="M7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N7" s="1">
         <f>SUM(O7:Q7)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" s="1">
         <v>1</v>
       </c>
-      <c r="P7" s="1"/>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
       <c r="Q7" s="1"/>
       <c r="R7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" s="1">
         <f>SUM(R7-S7)</f>
@@ -719,11 +728,11 @@
       </c>
       <c r="U7" s="1">
         <f>SUM((O7*3)+P7)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V7">
         <f>SUM(U7+T7*0.001+R7*0.00001)</f>
-        <v>3.00102</v>
+        <v>4.0010300000000001</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -838,24 +847,24 @@
       </c>
       <c r="N10" s="1">
         <f>SUM(O10:Q10)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1">
         <v>1</v>
       </c>
       <c r="Q10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S10" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T10" s="1">
         <f>SUM(R10-S10)</f>
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="U10" s="1">
         <f>SUM((O10*3)+P10)</f>
@@ -863,7 +872,7 @@
       </c>
       <c r="V10">
         <f>SUM(U10+T10*0.001+R10*0.00001)</f>
-        <v>0.99902000000000002</v>
+        <v>0.99704999999999999</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.3">
@@ -874,7 +883,9 @@
         <v>16</v>
       </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -959,27 +970,27 @@
     <row r="13" spans="2:22" x14ac:dyDescent="0.3">
       <c r="N13">
         <f>SUM(N4:N12)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O13">
         <f>SUM(O4:O12)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <f>SUM(P4:P12)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <f>SUM(Q4:Q12)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R13">
         <f>SUM(R4:R12)</f>
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="S13">
         <f>SUM(S4:S12)</f>
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="T13">
         <f>SUM(T4:T12)</f>
@@ -987,7 +998,7 @@
       </c>
       <c r="U13">
         <f>SUM(U4:U12)</f>
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="14:30" x14ac:dyDescent="0.3">
